--- a/converted_files/837/commercial.xlsx
+++ b/converted_files/837/commercial.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4e50</t>
+          <t>69e82c69836d7d05c9a05649</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2415,7 +2415,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4e50</t>
+          <t>69e82c69836d7d05c9a05649</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2800,7 +2800,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4e50</t>
+          <t>69e82c69836d7d05c9a05649</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/837/commercial.xlsx
+++ b/converted_files/837/commercial.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4e50</t>
+          <t>69efef06ad4799caa7f5e2cb</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2025,9 +2025,21 @@
       </c>
       <c r="BF2"/>
       <c r="BG2"/>
-      <c r="BH2"/>
-      <c r="BI2"/>
-      <c r="BJ2"/>
+      <c r="BH2" s="3" t="inlineStr">
+        <is>
+          <t>MAIMI</t>
+        </is>
+      </c>
+      <c r="BI2" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="BJ2" s="3" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
       <c r="BK2"/>
       <c r="BL2"/>
       <c r="BM2"/>
@@ -2049,9 +2061,21 @@
       </c>
       <c r="BR2"/>
       <c r="BS2"/>
-      <c r="BT2"/>
-      <c r="BU2"/>
-      <c r="BV2"/>
+      <c r="BT2" s="3" t="inlineStr">
+        <is>
+          <t>MAIMI</t>
+        </is>
+      </c>
+      <c r="BU2" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="BV2" s="3" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
       <c r="BW2" s="3" t="inlineStr">
         <is>
           <t>PROVIDER_COMMERCIAL_NUMBER</t>
@@ -2415,7 +2439,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4e50</t>
+          <t>69efef06ad4799caa7f5e2cb</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2800,7 +2824,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4e50</t>
+          <t>69efef06ad4799caa7f5e2cb</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/837/commercial.xlsx
+++ b/converted_files/837/commercial.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a05649</t>
+          <t>6a04cb3c618f76c4f7b194fa</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2415,7 +2415,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a05649</t>
+          <t>6a04cb3c618f76c4f7b194fa</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2800,7 +2800,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a05649</t>
+          <t>6a04cb3c618f76c4f7b194fa</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/837/commercial.xlsx
+++ b/converted_files/837/commercial.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b194fa</t>
+          <t>6a04cc5c1ef26d534baf4008</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2415,7 +2415,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b194fa</t>
+          <t>6a04cc5c1ef26d534baf4008</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2800,7 +2800,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b194fa</t>
+          <t>6a04cc5c1ef26d534baf4008</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/837/commercial.xlsx
+++ b/converted_files/837/commercial.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf4008</t>
+          <t>6a0614def8d6a2fc74348e52</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2415,7 +2415,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf4008</t>
+          <t>6a0614def8d6a2fc74348e52</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2800,7 +2800,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf4008</t>
+          <t>6a0614def8d6a2fc74348e52</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/837/commercial.xlsx
+++ b/converted_files/837/commercial.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348e52</t>
+          <t>6a32cb6497613a0e49909525</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2415,7 +2415,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348e52</t>
+          <t>6a32cb6497613a0e49909525</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2800,7 +2800,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348e52</t>
+          <t>6a32cb6497613a0e49909525</t>
         </is>
       </c>
       <c r="B4"/>
